--- a/www/download/IND.surplus_value.empe_hs.r.pc.zdW13.xlsx
+++ b/www/download/IND.surplus_value.empe_hs.r.pc.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>0.231852963089699</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>0.189882245889936</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>0.22732542338622</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>0.210856802996005</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>0.149359861564079</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>0.213341453348697</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>0.238434745717872</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>0.203724313521644</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>0.133667087137762</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-0.0321384469115149</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-0.0827251026309925</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-0.055268348152646</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-0.0665464243221511</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>0.0225044650630868</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>0.0699324514309512</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-0.254387602435953</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-22.48</t>
+          <t>-0.22477831652186</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-0.0623121834566422</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-0.0680564861846703</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-0.0671313568272218</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.00359373496684268</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.0141461519641489</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-0.0225585065925493</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-0.0705859625433588</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-13.64</t>
+          <t>-0.13636833960629</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-14.97</t>
+          <t>-0.149652780557772</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-17.65</t>
+          <t>-0.176451032552778</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-18.39</t>
+          <t>-0.183866585713138</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-0.222160339891396</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-16.09</t>
+          <t>-0.160932248796069</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-39.51</t>
+          <t>-0.39511289587557</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-40.63</t>
+          <t>-0.406318317075017</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-37.37</t>
+          <t>-0.373707475424568</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-36.66</t>
+          <t>-0.366621506752562</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-42.24</t>
+          <t>-0.422351413925135</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-43.25</t>
+          <t>-0.43251086785983</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-46.44</t>
+          <t>-0.464364246238836</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-50.02</t>
+          <t>-0.500183516055804</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-56.48</t>
+          <t>-0.564779004543441</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-61.33</t>
+          <t>-0.613293223587781</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-60.79</t>
+          <t>-0.607923466948342</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-60.39</t>
+          <t>-0.603884212202214</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-58.13</t>
+          <t>-0.58126525555079</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-52.64</t>
+          <t>-0.526411777454433</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-55.2</t>
+          <t>-0.551979183828285</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>165.49</t>
+          <t>1.65491879138928</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>208.04</t>
+          <t>2.08038308932218</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>248.44</t>
+          <t>2.48442944376938</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>144.62</t>
+          <t>1.44619295855625</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>162.43</t>
+          <t>1.62433340304938</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>153.85</t>
+          <t>1.53846747871379</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>146.15</t>
+          <t>1.46152668977426</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>141.69</t>
+          <t>1.41689320032648</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>211.57</t>
+          <t>2.11571813813313</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>153.19</t>
+          <t>1.53191681406483</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>160.11</t>
+          <t>1.60112491568941</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>1.69767423334085</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>169.74</t>
+          <t>1.6973900872426</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>140.82</t>
+          <t>1.40821051216524</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>124.84</t>
+          <t>1.24842912228583</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-20.01</t>
+          <t>-0.200056700722833</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-18.64</t>
+          <t>-0.186445745655546</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-0.119537190513819</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.1</t>
+          <t>-0.120991899681693</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.0392497422952316</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>0.0613238547205619</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>0.134175231762371</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>0.180895675210068</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>0.245307522209838</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>0.268166504288446</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>0.244372770390011</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>0.288623776904714</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>0.338693393185769</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>0.340409664600624</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>0.412375964420345</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>63.17</t>
+          <t>0.631665321018867</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>0.634074140571407</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>0.703163023415521</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>0.58757299740433</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>0.501515395591299</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>0.387925197597521</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>0.296295460012828</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>0.276601643596048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>0.208153215205554</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.170734665699881</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>0.103536744978086</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>0.0631161792455519</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>0.12155334344045</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>0.147471180408575</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>0.276965536536607</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-44.21</t>
+          <t>-0.442062615235115</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-41.73</t>
+          <t>-0.417311564605445</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-44.26</t>
+          <t>-0.442624142554934</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-46.1</t>
+          <t>-0.461032576023667</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-46.97</t>
+          <t>-0.469658005673531</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-46.22</t>
+          <t>-0.462246953591048</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-42.26</t>
+          <t>-0.422551365931953</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-40.24</t>
+          <t>-0.402395866957598</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-38.15</t>
+          <t>-0.381455097119571</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-32.68</t>
+          <t>-0.326817921991565</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-29.1</t>
+          <t>-0.291044522066011</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-28.92</t>
+          <t>-0.289224323740046</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-0.228221103662421</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-23.36</t>
+          <t>-0.233612474279113</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-21.14</t>
+          <t>-0.211399892120848</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>49.36</t>
+          <t>0.493623441827055</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.01</t>
+          <t>0.460065500906883</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>66.93</t>
+          <t>0.669270840809346</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>56.39</t>
+          <t>0.563856066707982</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>0.440062605036318</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>0.45636742650405</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>0.36783292999725</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>0.350212378415792</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>0.223111535603099</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>0.209344031557566</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>0.224013646635447</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>0.24456459472611</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>0.40083797277373</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>0.200110709486781</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>0.42549355718445</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>201.6</t>
+          <t>2.01603590357203</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>1.12416761594042</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>135.4</t>
+          <t>1.35403188994062</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>129.19</t>
+          <t>1.29188595315727</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>129.62</t>
+          <t>1.29615204210999</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>139.14</t>
+          <t>1.39137348442416</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>115.61</t>
+          <t>1.15614460168806</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>108.01</t>
+          <t>1.08007542907705</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>107.99</t>
+          <t>1.07985256906632</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>0.745475644130422</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>0.691182866627557</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>74.63</t>
+          <t>0.746297846440201</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0.701678150927227</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>69.26</t>
+          <t>0.692617999031871</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>0.929102196064292</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>-0.303766356481106</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-23.96</t>
+          <t>-0.239629593858325</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>-0.136155346657057</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-0.150073975747319</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-0.15624432456782</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-20.63</t>
+          <t>-0.206264851981382</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-0.185235444349331</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-19.15</t>
+          <t>-0.191454313173613</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-0.296928648534534</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-29.45</t>
+          <t>-0.294522497448843</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-27.23</t>
+          <t>-0.272268352642504</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-0.293410364870604</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-31.24</t>
+          <t>-0.312354051700689</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-30.46</t>
+          <t>-0.304633552802611</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>-0.275417472368968</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-20.05</t>
+          <t>-0.200484937214673</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-17.59</t>
+          <t>-0.175888628368051</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>0.163044298052595</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.00603635812315817</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.00962974264462113</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0222357637446757</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-0.0239560174711231</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-0.0518456136736412</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-0.178926030422914</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-18.39</t>
+          <t>-0.183872861794268</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-0.167577355366778</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-17.4</t>
+          <t>-0.173962023946933</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-17.81</t>
+          <t>-0.178091692472775</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-14.8</t>
+          <t>-0.148039362024105</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-0.0653711483797682</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>0.0846624584755993</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>0.165910748044423</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>0.400916274821248</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>0.300912571859787</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>0.245567723790415</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>0.335085313508086</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>0.257081941718835</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>0.202314586511662</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.170232231266098</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>0.0612370100447697</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>0.063550033132705</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0.0546759248869224</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>0.0701922683311171</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>0.0606835075088397</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>0.182700940617201</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>208.82</t>
+          <t>2.08823012713005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>184.26</t>
+          <t>1.84258697932394</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>174.71</t>
+          <t>1.74714048261401</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>152.43</t>
+          <t>1.52425320234345</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>152.98</t>
+          <t>1.52983985189505</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>117.91</t>
+          <t>1.17909390567868</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>127.42</t>
+          <t>1.27421074379771</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>84.68</t>
+          <t>0.84682232276026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>63.93</t>
+          <t>0.639271287468497</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>0.553973195162482</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>71.22</t>
+          <t>0.712198221587406</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>76.94</t>
+          <t>0.769440918646436</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>79.24</t>
+          <t>0.792379448014598</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>64.28</t>
+          <t>0.642809289715679</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>76.57</t>
+          <t>0.765706782407008</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>0.301160811196562</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>0.246570225821216</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>0.49850126828304</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>0.38329421310145</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>0.341487554270957</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>0.469579987282757</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>0.451748200565832</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>0.428255619208067</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>0.335689114230479</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>0.209274252428532</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>17.49</t>
+          <t>0.174863641077785</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>0.132406752516898</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>0.115929016570369</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>0.0726185291787917</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>13.53</t>
+          <t>0.135341487303143</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-0.0953946978857368</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-9.55</t>
+          <t>-0.0954988528258677</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>0.0988002505942491</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.00930750544846493</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-0.0537375182286192</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-0.0632329716856137</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>-0.11376728085196</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-14.27</t>
+          <t>-0.142688507549152</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-0.148619415569282</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-0.209718356558716</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-19.94</t>
+          <t>-0.199357481867082</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-0.168387820578365</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-15.66</t>
+          <t>-0.156572224837471</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-16.72</t>
+          <t>-0.167187686871967</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-10.09</t>
+          <t>-0.100873225743932</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>0.242579848653186</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>0.206766189782657</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>0.319774635409042</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>0.208660758298861</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>0.159727763465677</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>0.10618111762126</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.0594880202854624</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.0348785448388818</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-0.0427285276395101</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-0.0973566324881681</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-8.88</t>
+          <t>-0.0888463798433009</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-0.08981655364785</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-0.0523688074023559</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>0.0206325681105959</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>0.138169587847801</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>0.703766599461967</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>63.93</t>
+          <t>0.639331417343689</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>65.44</t>
+          <t>0.65439702214624</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>0.723527504865276</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>62.81</t>
+          <t>0.628122837586518</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>0.554117395203458</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>57.79</t>
+          <t>0.577854658531249</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>0.403113658537376</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>0.441513274957339</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>0.434853168685535</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>0.485467688900439</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>0.543864759191402</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>0.472684977235068</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>0.440836234251984</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>0.420101126579223</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>74.05</t>
+          <t>0.740546465933285</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>0.758595790064499</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>84.23</t>
+          <t>0.842338052536279</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>86.16</t>
+          <t>0.861614162162573</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>82.43</t>
+          <t>0.824329219953458</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>0.802096424399107</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>85.34</t>
+          <t>0.853395297513937</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>0.700296761376969</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>78.37</t>
+          <t>0.783661355393147</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>84.37</t>
+          <t>0.843670931888275</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>0.865439739277316</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>0.967039452737084</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>0.892782853224792</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>91.77</t>
+          <t>0.917681301150516</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>110.83</t>
+          <t>1.10834933628711</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-0.0206539311815502</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>0.197591654417817</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>0.508502986258184</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>0.838655523201535</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>126.65</t>
+          <t>1.2664756668792</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>51.27</t>
+          <t>0.512702199567699</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>0.461014777544591</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>0.465076815268635</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>25.68</t>
+          <t>0.256801121620594</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>0.388911630162605</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.0167995630360112</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-0.0488505179213964</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-0.18346777405289</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-0.150006663649459</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-18.08</t>
+          <t>-0.180772669801084</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-53.44</t>
+          <t>-0.534386503182087</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-48.63</t>
+          <t>-0.486318980683689</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-50.66</t>
+          <t>-0.506610233373691</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-51.49</t>
+          <t>-0.514880047969322</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-50.37</t>
+          <t>-0.503689087683467</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-50.51</t>
+          <t>-0.50513191246334</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-50.13</t>
+          <t>-0.501326791619559</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-47.38</t>
+          <t>-0.473846085747265</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-49.4</t>
+          <t>-0.493999250781953</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-50.31</t>
+          <t>-0.503112127539162</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-51.3</t>
+          <t>-0.512971865719958</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-51.8</t>
+          <t>-0.517985473568084</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-48.14</t>
+          <t>-0.481420856067522</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-45.73</t>
+          <t>-0.457299482709058</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-47.28</t>
+          <t>-0.472822027674888</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>38.62</t>
+          <t>0.3862069215743</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>0.370488683648112</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>0.548379926654479</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.87</t>
+          <t>0.618659074629933</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>0.63618044567296</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>59.96</t>
+          <t>0.599551173226395</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>0.409337370902162</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>0.335587168064942</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>0.485539682974211</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>0.590000392372741</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>0.395542192713526</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>32.06</t>
+          <t>0.320627043863354</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>0.255766731155261</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>0.186503980903638</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>0.107561565586113</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-0.0351275985657629</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-0.031874711805159</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>0.0463926618780335</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>0.0543895492547086</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>0.0634540537563089</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>0.0225073834510612</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.0263766154445118</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>0.0287765194323679</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.000774592542623465</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-10.07</t>
+          <t>-0.100731587754584</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-0.0633609129035049</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-0.0495287228222665</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>0.0449512839811184</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>0.0702505429823594</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>0.162605432360634</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-0.0519368628734533</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>0.0807089141820116</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>0.227459367978105</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>0.263415725034783</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>0.203781833303496</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>0.153747268445099</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>0.165864440694659</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>0.205795470492231</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>0.199451339490104</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>0.122708446362214</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>0.121157504673718</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>0.183962289710101</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>0.313571312821168</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>0.350567248614527</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>30.21</t>
+          <t>0.302120048343019</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>0.232837333815162</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>0.293371118669087</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>0.44886329900202</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.17</t>
+          <t>0.611686362007122</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>71.97</t>
+          <t>0.719728415146376</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>65.62</t>
+          <t>0.656232349204733</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>62.22</t>
+          <t>0.6221685371057</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>66.76</t>
+          <t>0.66763408392319</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>0.567083687484913</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>0.579714596804882</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>54.79</t>
+          <t>0.547887846975015</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>0.502312814337336</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>53.63</t>
+          <t>0.5362901309923</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>66.32</t>
+          <t>0.663212183071626</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>0.755434868224492</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>159.61</t>
+          <t>1.59610272422646</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>144.59</t>
+          <t>1.44594282480374</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>1.47599318357159</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>97.69</t>
+          <t>0.976940312088795</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>89.34</t>
+          <t>0.893393417392551</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>92.76</t>
+          <t>0.927598057496928</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>99.14</t>
+          <t>0.991380526723325</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>90.88</t>
+          <t>0.908832260562732</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>83.47</t>
+          <t>0.834690735610148</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>108.27</t>
+          <t>1.08274539924991</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>1.08684210035247</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>1.03143132201443</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>123.88</t>
+          <t>1.2387591957267</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>106.36</t>
+          <t>1.06357079173401</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>113.25</t>
+          <t>1.13252914924912</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.0125107262164277</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>0.150373639765347</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>0.400166258616092</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>0.325716332387166</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>0.210633676835515</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>0.10595169192767</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>0.214349800678459</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>0.132944309358396</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>0.164837445140973</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>0.0711703566839017</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>0.0257093196138374</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>0.0446606676414067</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>0.221981514658638</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>0.0604360758033184</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>0.258229491368663</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>183.22</t>
+          <t>1.83216405819129</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>172.6</t>
+          <t>1.72604793818091</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>166.17</t>
+          <t>1.66167229389738</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>151.92</t>
+          <t>1.51919557948801</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>149.56</t>
+          <t>1.49555410611716</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>1.80296583873909</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>188.09</t>
+          <t>1.88086596770023</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>195.23</t>
+          <t>1.95227391288271</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>195.26</t>
+          <t>1.95256863709825</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>181.91</t>
+          <t>1.81909875791064</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>176.52</t>
+          <t>1.76517322803189</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>159.76</t>
+          <t>1.59759908976462</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>132.81</t>
+          <t>1.32810789955337</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>97.42</t>
+          <t>0.974194891028137</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>117.48</t>
+          <t>1.17480431481062</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>123.1</t>
+          <t>1.23096075349854</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>138.54</t>
+          <t>1.38535177765049</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>158.52</t>
+          <t>1.58515436141514</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>136.28</t>
+          <t>1.36281463820022</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>122.41</t>
+          <t>1.2241290296451</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>117.58</t>
+          <t>1.17575355004671</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>0.990950467806924</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>100.48</t>
+          <t>1.00475161680738</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>0.98154365767428</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>107.84</t>
+          <t>1.07836536291816</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>139.32</t>
+          <t>1.39322173253761</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>139.99</t>
+          <t>1.39990942907205</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>147.45</t>
+          <t>1.4745063855384</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>154.23</t>
+          <t>1.54231023090058</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>156.64</t>
+          <t>1.56637886420426</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>0.468663619917496</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>0.330873535503753</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>0.616429319359475</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>0.492022842539342</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>0.314064676725371</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>0.226060481868569</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-0.0921672776868417</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.00101849364673345</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>0.112683138625561</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>0.211127688364792</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>0.161037472324486</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.211545426962293</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>0.128440915057582</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>0.0769618821268754</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>0.200946361248206</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-0.399955374550369</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-35.64</t>
+          <t>-0.356400026444354</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-0.052521867989316</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-23.58</t>
+          <t>-0.235790186151698</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-27.42</t>
+          <t>-0.274235655246023</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-26.2</t>
+          <t>-0.261994115744007</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-0.342561435381653</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-41.35</t>
+          <t>-0.413517303321499</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-35.56</t>
+          <t>-0.355621767250763</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-38.1</t>
+          <t>-0.380984731479343</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-36.38</t>
+          <t>-0.363761623114895</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-36.71</t>
+          <t>-0.36712412106086</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-34.2</t>
+          <t>-0.34203495244387</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-40.36</t>
+          <t>-0.403578533237469</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-38.2</t>
+          <t>-0.382034252074961</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>0.14126837050638</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>0.101248130333154</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>0.0956604409732689</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>0.0798163273081232</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>0.16882577984387</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>0.220323241474966</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>54.56</t>
+          <t>0.545557585975063</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>0.578109458628202</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>0.821129445630835</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>83.09</t>
+          <t>0.830897632393204</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>0.807061761641309</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>0.875597110445008</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>0.883800061156756</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>77.18</t>
+          <t>0.771759419007131</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>101.41</t>
+          <t>1.01409168656285</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-15.66</t>
+          <t>-0.156644309305321</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-0.168677291066367</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-0.0558084944644722</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-15.46</t>
+          <t>-0.154575593384568</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-0.146422545510436</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-15.58</t>
+          <t>-0.15580952235066</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-18.08</t>
+          <t>-0.180839884135245</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-0.162593349136316</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>0.0420504026750705</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-12.38</t>
+          <t>-0.123775485717322</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-0.107608772004533</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0384792568464014</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>0.0893287512324119</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>0.0738700806233468</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>0.210573931436046</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>58.71</t>
+          <t>0.587142925095267</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>60.97</t>
+          <t>0.60966271538514</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>0.681959316478895</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>0.451252778159967</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>0.0868521935019906</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.00650016396519126</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0228291366194389</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>0.372605852552688</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>74.86</t>
+          <t>0.748596665801427</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>62.05</t>
+          <t>0.620510965869712</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>0.438892684316792</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>0.489394858792249</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>0.452509065053673</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>38.41</t>
+          <t>0.384065556127337</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>53.68</t>
+          <t>0.536793408103705</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>0.355194748714959</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>0.319024967309024</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0.380016232318351</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>0.478138367511221</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>0.614092984900922</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>45.08</t>
+          <t>0.450816401306429</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>0.436508997828017</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>0.356787185677967</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>0.221251720625699</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>0.191353395012816</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>0.123127527979709</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>0.112708372811425</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.000422487321483089</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-0.168901409872909</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>-19.83</t>
+          <t>-0.198260131143294</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>278.87</t>
+          <t>2.78866602121676</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>242.35</t>
+          <t>2.4235227214585</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>261.01</t>
+          <t>2.61007742197025</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>265.17</t>
+          <t>2.65170605659432</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>273.26</t>
+          <t>2.73256881139954</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>252.02</t>
+          <t>2.52017186384376</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>254.53</t>
+          <t>2.54527045059635</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>264.89</t>
+          <t>2.64890703046743</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>229.43</t>
+          <t>2.29426191022507</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>146.64</t>
+          <t>1.46642145684894</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>144.89</t>
+          <t>1.44887877754333</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>127.76</t>
+          <t>1.27758650933209</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>103.41</t>
+          <t>1.03411879363749</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>105.04</t>
+          <t>1.05038151304799</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>72.56</t>
+          <t>0.725636649973505</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-0.082127456077376</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-0.0466404675041922</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>0.0815766088716274</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>0.0285376986011805</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>0.0538781114807676</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>0.0288216882805246</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-0.0403409420939785</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.0201546501955667</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-0.0869073067598637</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-0.0210322652159942</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.03383983124266</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>0.090664711463929</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>0.13098922966922</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-18.23</t>
+          <t>-0.182293006483285</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-17.26</t>
+          <t>-0.172641533998085</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>0.141478044643975</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>0.123746949880494</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>0.319934388215686</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>0.230620333036318</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>0.220750197807577</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>0.150221711986649</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>0.144530209183577</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0888875352483953</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>0.0484848190614646</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.00575530577395322</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.0302605767247662</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.017641618354067</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-0.0314297250240264</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.0183605815872827</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>0.164330807700162</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>0.334193373537382</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>0.214862516155532</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>0.188799069038954</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>0.211038199755584</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>0.0580451432450739</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>27.99</t>
+          <t>0.279896671839015</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>0.347346048454413</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>0.585410315850558</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>55.73</t>
+          <t>0.557303666104189</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>0.463152225457605</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>66.04</t>
+          <t>0.660427114969611</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>0.765602885582663</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>79.65</t>
+          <t>0.796543455456845</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0378004082460583</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>0.168482115113238</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>0.1866382665247</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>0.125934157886341</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>0.26702723829381</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>0.335171437918001</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>38.62</t>
+          <t>0.386176184994201</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>0.317879321557897</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>0.301227610108251</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>0.350492885023236</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>0.352587966334417</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>0.3913108453322</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>0.445007532684214</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>50.76</t>
+          <t>0.507573159819634</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>0.710133533653967</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>73.42</t>
+          <t>0.734174721905161</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>0.950058505868863</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>0.375255079211334</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>0.405078012858743</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>0.38662181133088</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>30.03</t>
+          <t>0.300296353910273</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>0.26774924786346</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>0.105919515923159</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>0.052369154710814</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.0300383210885871</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.00722911558617212</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-0.0412212922787144</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-0.040336201476442</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.0223792304579357</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>0.0791989717296291</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>14.44</t>
+          <t>0.144354036354639</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>0.171003381266036</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-61.74</t>
+          <t>-0.617401796089394</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-58.89</t>
+          <t>-0.588920461797345</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-58.5</t>
+          <t>-0.585013268959882</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-59.3</t>
+          <t>-0.593006362370251</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-60.47</t>
+          <t>-0.604652697230394</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-60.17</t>
+          <t>-0.601676588556694</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-58.43</t>
+          <t>-0.584259736512084</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-58.72</t>
+          <t>-0.587244789412835</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-55.5</t>
+          <t>-0.555043573549589</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-52.49</t>
+          <t>-0.52487497870046</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>-52.85</t>
+          <t>-0.52854004245487</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>-52.36</t>
+          <t>-0.523612040494736</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>-47.06</t>
+          <t>-0.470634148761849</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>-43.88</t>
+          <t>-0.438810075381364</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>-43.88</t>
+          <t>-0.438799369490669</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-33.51</t>
+          <t>-0.335089360283051</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-0.299865152396016</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-28.55</t>
+          <t>-0.285467089813862</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-0.296504503082111</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-30.35</t>
+          <t>-0.303544222196153</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-32.29</t>
+          <t>-0.322911800648971</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-0.32143189986335</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-0.319639556464029</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-31.43</t>
+          <t>-0.314280136721243</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-30.81</t>
+          <t>-0.308138197665157</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-31.16</t>
+          <t>-0.311643006534921</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-30.71</t>
+          <t>-0.30709101656536</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-0.25693608988939</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-0.236715634258558</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-0.235509867924651</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
